--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/lib-gral-bdo-o-higgins.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/lib-gral-bdo-o-higgins.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>14000.25</v>
+        <v>13928.32</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>11477.8</v>
+        <v>11418.83</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1068.72</v>
+        <v>1063.23</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>12824.66</v>
+        <v>12758.76</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9665.52</v>
+        <v>9615.85</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>70535.62</v>
+        <v>69831.66</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6162.23</v>
+        <v>6100.73</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2137.44</v>
+        <v>2115.06</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>41829.76</v>
+        <v>41391.71</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4365.73</v>
+        <v>4320.01</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>11755.94</v>
+        <v>11691.68</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>64447.83</v>
+        <v>63729.79</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>213.74</v>
+        <v>212.57</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>4274.89</v>
+        <v>4269.45</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>8155.28</v>
+        <v>8144.9</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6282.59</v>
+        <v>6350.92</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>89066.03999999999</v>
+        <v>89358.98</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>11909.68</v>
+        <v>12115.26</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>10687.22</v>
+        <v>10871.69</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>8801.66</v>
+        <v>8953.59</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>22443.15</v>
+        <v>22604.95</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3527.1</v>
+        <v>3552.53</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>4274.89</v>
+        <v>4296.96</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1816.82</v>
+        <v>1826.21</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>9404.75</v>
+        <v>9453.32</v>
       </c>
     </row>
     <row r="27">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>48275.35</v>
+        <v>48524.66</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>7249.14</v>
+        <v>7286.58</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>8020.68</v>
+        <v>7940.88</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5602.07</v>
+        <v>5546.33</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1375.3</v>
+        <v>1370.37</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>218.3</v>
+        <v>217.52</v>
       </c>
     </row>
     <row r="33">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>12552.35</v>
+        <v>12507.34</v>
       </c>
     </row>
     <row r="34">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>16372.63</v>
+        <v>16303.99</v>
       </c>
     </row>
     <row r="35">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2239.78</v>
+        <v>2230.39</v>
       </c>
     </row>
     <row r="36">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>61233.64</v>
+        <v>60976.94</v>
       </c>
     </row>
     <row r="37">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>30081.98</v>
+        <v>29733.84</v>
       </c>
     </row>
     <row r="38">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2281.25</v>
+        <v>2290.01</v>
       </c>
     </row>
     <row r="39">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>570.3099999999999</v>
+        <v>572.5</v>
       </c>
     </row>
     <row r="40">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>10502.06</v>
+        <v>10549.65</v>
       </c>
     </row>
     <row r="41">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>25293.75</v>
+        <v>25408.37</v>
       </c>
     </row>
     <row r="42">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>771.2</v>
+        <v>770.12</v>
       </c>
     </row>
     <row r="43">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>11538.34</v>
+        <v>11522.15</v>
       </c>
     </row>
     <row r="44">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>14190.43</v>
+        <v>14170.53</v>
       </c>
     </row>
     <row r="45">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1077.89</v>
+        <v>1079.27</v>
       </c>
     </row>
     <row r="46">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1637.26</v>
+        <v>1648.53</v>
       </c>
     </row>
     <row r="47">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2837.92</v>
+        <v>2857.46</v>
       </c>
     </row>
     <row r="48">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>6416.54</v>
+        <v>6460.71</v>
       </c>
     </row>
     <row r="49">
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>76382.10000000001</v>
+        <v>77201.42</v>
       </c>
     </row>
     <row r="50">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>16372.63</v>
+        <v>16573.85</v>
       </c>
     </row>
     <row r="51">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>49782.73</v>
+        <v>50422.42</v>
       </c>
     </row>
     <row r="52">
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>22921.69</v>
+        <v>23047.04</v>
       </c>
     </row>
     <row r="53">
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>10231.17</v>
+        <v>9969.91</v>
       </c>
     </row>
     <row r="54">
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>29414.6</v>
+        <v>28840.89</v>
       </c>
     </row>
     <row r="55">
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1131.27</v>
+        <v>1104.8</v>
       </c>
     </row>
     <row r="56">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>6234.24</v>
+        <v>6088.4</v>
       </c>
     </row>
     <row r="57">
@@ -3932,7 +3932,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>9050.120000000001</v>
+        <v>8920.41</v>
       </c>
     </row>
     <row r="58">
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>13010.21</v>
+        <v>12823.73</v>
       </c>
     </row>
     <row r="59">
@@ -4054,7 +4054,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>11837.46</v>
+        <v>11814.15</v>
       </c>
     </row>
     <row r="60">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>11510.06</v>
+        <v>11502.2</v>
       </c>
     </row>
     <row r="61">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>52630.49</v>
+        <v>52449.85</v>
       </c>
     </row>
     <row r="62">
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>77283.37</v>
+        <v>76875.12</v>
       </c>
     </row>
     <row r="63">
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3620.05</v>
+        <v>3643.78</v>
       </c>
     </row>
     <row r="64">
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1244.39</v>
+        <v>1252.55</v>
       </c>
     </row>
     <row r="65">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>6650.26</v>
+        <v>6739.81</v>
       </c>
     </row>
     <row r="66">
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>11312.66</v>
+        <v>11465</v>
       </c>
     </row>
     <row r="67">
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>36200.5</v>
+        <v>36687.99</v>
       </c>
     </row>
     <row r="68">
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1182.17</v>
+        <v>1200.17</v>
       </c>
     </row>
     <row r="69">
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>15837.85</v>
+        <v>16078.96</v>
       </c>
     </row>
     <row r="70">
@@ -4729,7 +4729,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>24887.84</v>
+        <v>25266.74</v>
       </c>
     </row>
     <row r="71">
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>26019.11</v>
+        <v>26651.84</v>
       </c>
     </row>
     <row r="72">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2828.16</v>
+        <v>2899.66</v>
       </c>
     </row>
     <row r="73">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>10103.28</v>
+        <v>10409.64</v>
       </c>
     </row>
     <row r="74">
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>49909.82</v>
+        <v>51393.29</v>
       </c>
     </row>
     <row r="75">
@@ -5034,7 +5034,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>12443.92</v>
+        <v>12813.79</v>
       </c>
     </row>
     <row r="76">
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>7480.2</v>
+        <v>7453.57</v>
       </c>
     </row>
     <row r="77">
@@ -5156,7 +5156,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1160.07</v>
+        <v>1151.38</v>
       </c>
     </row>
     <row r="78">
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>13236.51</v>
+        <v>13180.7</v>
       </c>
     </row>
     <row r="79">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>13114.54</v>
+        <v>13150.55</v>
       </c>
     </row>
     <row r="80">
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>9152.969999999999</v>
+        <v>9216.700000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5404,7 +5404,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>6324.47</v>
+        <v>6313.63</v>
       </c>
     </row>
     <row r="82">
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>110797.1</v>
+        <v>110634.11</v>
       </c>
     </row>
     <row r="83">
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>16239.74</v>
+        <v>16151.3</v>
       </c>
     </row>
     <row r="84">
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>6819.56</v>
+        <v>6779.38</v>
       </c>
     </row>
     <row r="85">
@@ -5652,7 +5652,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>9835.91</v>
+        <v>9797.950000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5713,7 +5713,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>13920.79</v>
+        <v>13867.06</v>
       </c>
     </row>
     <row r="87">
@@ -5774,7 +5774,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>54523.1</v>
+        <v>54312.66</v>
       </c>
     </row>
     <row r="88">
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>13114.54</v>
+        <v>13182.44</v>
       </c>
     </row>
     <row r="89">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>52534.61</v>
+        <v>52806.6</v>
       </c>
     </row>
     <row r="90">
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2923.42</v>
+        <v>3052.53</v>
       </c>
     </row>
     <row r="91">
@@ -6018,7 +6018,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>25277.69</v>
+        <v>26394.01</v>
       </c>
     </row>
     <row r="92">
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>5813.21</v>
+        <v>5836.13</v>
       </c>
     </row>
     <row r="93">
@@ -6140,7 +6140,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>13188.4</v>
+        <v>13240.39</v>
       </c>
     </row>
     <row r="94">
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>445.11</v>
+        <v>446.2</v>
       </c>
     </row>
     <row r="95">
@@ -6262,7 +6262,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>11500.15</v>
+        <v>11418.99</v>
       </c>
     </row>
     <row r="96">
@@ -6323,7 +6323,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2198.06</v>
+        <v>2237.91</v>
       </c>
     </row>
     <row r="97">
@@ -6388,7 +6388,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>79462.17</v>
+        <v>79005.72</v>
       </c>
     </row>
     <row r="98">
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>6460.76</v>
+        <v>6423.65</v>
       </c>
     </row>
     <row r="99">
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>46159.38</v>
+        <v>45863.66</v>
       </c>
     </row>
     <row r="100">
@@ -6571,7 +6571,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>10995.71</v>
+        <v>10948.34</v>
       </c>
     </row>
     <row r="101">
@@ -6632,7 +6632,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>13188.36</v>
+        <v>13131.55</v>
       </c>
     </row>
     <row r="102">
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1044.52</v>
+        <v>1029.41</v>
       </c>
     </row>
     <row r="103">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>50179.94</v>
+        <v>49453.98</v>
       </c>
     </row>
     <row r="104">
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>39565.08</v>
+        <v>38992.69</v>
       </c>
     </row>
     <row r="105">
@@ -6876,7 +6876,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>10250.24</v>
+        <v>10029.71</v>
       </c>
     </row>
     <row r="106">
@@ -6937,7 +6937,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>5495.15</v>
+        <v>5367.28</v>
       </c>
     </row>
     <row r="107">
@@ -6998,7 +6998,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>24501.99</v>
+        <v>23856.77</v>
       </c>
     </row>
     <row r="108">
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>5184.39</v>
+        <v>5090.37</v>
       </c>
     </row>
     <row r="109">
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>6727.94</v>
+        <v>6605.93</v>
       </c>
     </row>
     <row r="110">
@@ -7181,7 +7181,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>12590.68</v>
+        <v>12253.55</v>
       </c>
     </row>
     <row r="111">
@@ -7242,7 +7242,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>13383.9</v>
+        <v>13422.86</v>
       </c>
     </row>
     <row r="112">
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1058.04</v>
+        <v>1062.44</v>
       </c>
     </row>
     <row r="113">
@@ -7364,7 +7364,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>11653.94</v>
+        <v>11702.37</v>
       </c>
     </row>
     <row r="114">
@@ -7425,7 +7425,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2962.51</v>
+        <v>2974.83</v>
       </c>
     </row>
     <row r="115">
@@ -7486,7 +7486,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>9946.639999999999</v>
+        <v>10076.44</v>
       </c>
     </row>
     <row r="116">
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>6449.82</v>
+        <v>6608.54</v>
       </c>
     </row>
     <row r="117">
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>4454.91</v>
+        <v>4505.57</v>
       </c>
     </row>
     <row r="118">
@@ -7669,7 +7669,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>6547.15</v>
+        <v>6589.03</v>
       </c>
     </row>
     <row r="119">
@@ -7730,7 +7730,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>17815.82</v>
+        <v>17871.87</v>
       </c>
     </row>
     <row r="120">
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>25615.72</v>
+        <v>25696.32</v>
       </c>
     </row>
     <row r="121">
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>76034.59</v>
+        <v>76349.73</v>
       </c>
     </row>
     <row r="122">
@@ -7917,7 +7917,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>46776.53</v>
+        <v>46970.41</v>
       </c>
     </row>
     <row r="123">
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>51185.96</v>
+        <v>51398.12</v>
       </c>
     </row>
     <row r="124">
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>9702.799999999999</v>
+        <v>9644.65</v>
       </c>
     </row>
     <row r="125">
@@ -8100,7 +8100,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>6274.29</v>
+        <v>6188.99</v>
       </c>
     </row>
     <row r="126">
@@ -8161,7 +8161,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1659.47</v>
+        <v>1636.91</v>
       </c>
     </row>
     <row r="127">
@@ -8222,7 +8222,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>16710.53</v>
+        <v>16568</v>
       </c>
     </row>
     <row r="128">
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2857.5</v>
+        <v>2889.46</v>
       </c>
     </row>
     <row r="129">
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>13375</v>
+        <v>13524.59</v>
       </c>
     </row>
     <row r="130">
@@ -8405,7 +8405,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>12594.17</v>
+        <v>12641.88</v>
       </c>
     </row>
     <row r="131">
@@ -8466,7 +8466,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>334.21</v>
+        <v>335.48</v>
       </c>
     </row>
     <row r="132">
@@ -8527,7 +8527,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>10026.31</v>
+        <v>10101.01</v>
       </c>
     </row>
     <row r="133">
@@ -8588,7 +8588,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>11657.16</v>
+        <v>11606.06</v>
       </c>
     </row>
     <row r="134">
@@ -8649,7 +8649,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>6548.97</v>
+        <v>6520.26</v>
       </c>
     </row>
     <row r="135">
@@ -8710,7 +8710,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>50434.36</v>
+        <v>50601.66</v>
       </c>
     </row>
     <row r="136">
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>80282.56</v>
+        <v>80538.08</v>
       </c>
     </row>
     <row r="137">
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>46789.47</v>
+        <v>46938.39</v>
       </c>
     </row>
     <row r="138">
@@ -8897,7 +8897,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>14482.45</v>
+        <v>14528.55</v>
       </c>
     </row>
     <row r="139">
@@ -8958,7 +8958,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>9004.83</v>
+        <v>9052.709999999999</v>
       </c>
     </row>
     <row r="140">
@@ -9019,7 +9019,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>16712.46</v>
+        <v>16801.32</v>
       </c>
     </row>
     <row r="141">
@@ -9080,7 +9080,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>24352.87</v>
+        <v>24701.34</v>
       </c>
     </row>
     <row r="142">
@@ -9141,7 +9141,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>11921.79</v>
+        <v>12092.38</v>
       </c>
     </row>
     <row r="143">
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>46491.84</v>
+        <v>47037.22</v>
       </c>
     </row>
     <row r="144">
@@ -9263,7 +9263,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>6175.98</v>
+        <v>6248.43</v>
       </c>
     </row>
     <row r="145">
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>12619.21</v>
+        <v>12832.64</v>
       </c>
     </row>
     <row r="146">
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>13284.42</v>
+        <v>13419.51</v>
       </c>
     </row>
     <row r="147">
@@ -9446,7 +9446,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>12514.05</v>
+        <v>12631.43</v>
       </c>
     </row>
     <row r="148">
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>496.8</v>
+        <v>488.4</v>
       </c>
     </row>
     <row r="149">
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>6641.69</v>
+        <v>6547.43</v>
       </c>
     </row>
     <row r="150">
@@ -9629,7 +9629,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>3320.84</v>
+        <v>3273.71</v>
       </c>
     </row>
     <row r="151">
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>6507.31</v>
+        <v>6414.95</v>
       </c>
     </row>
     <row r="152">
@@ -9751,7 +9751,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>99.63</v>
+        <v>99.01000000000001</v>
       </c>
     </row>
     <row r="153">
@@ -9812,7 +9812,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>16603.65</v>
+        <v>16679.05</v>
       </c>
     </row>
     <row r="154">
@@ -9873,7 +9873,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>19925.07</v>
+        <v>20303.88</v>
       </c>
     </row>
     <row r="155">
@@ -9934,7 +9934,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>553.5</v>
+        <v>565.98</v>
       </c>
     </row>
     <row r="156">
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>13339.31</v>
+        <v>13304.02</v>
       </c>
     </row>
     <row r="157">
@@ -10056,7 +10056,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>52850.79</v>
+        <v>52146.81</v>
       </c>
     </row>
     <row r="158">
@@ -10117,7 +10117,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>11455.59</v>
+        <v>11231.36</v>
       </c>
     </row>
     <row r="159">
@@ -10178,7 +10178,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>16604.23</v>
+        <v>16279.22</v>
       </c>
     </row>
     <row r="160">
@@ -10243,7 +10243,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>81986.28999999999</v>
+        <v>80771.59</v>
       </c>
     </row>
     <row r="161">
@@ -10304,7 +10304,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>24352.87</v>
+        <v>23992.06</v>
       </c>
     </row>
     <row r="162">
@@ -10365,7 +10365,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>13296.51</v>
+        <v>13023.25</v>
       </c>
     </row>
     <row r="163">
@@ -10426,7 +10426,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>9595.469999999999</v>
+        <v>9686.610000000001</v>
       </c>
     </row>
     <row r="164">
@@ -10487,7 +10487,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>9666.190000000001</v>
+        <v>9758.01</v>
       </c>
     </row>
     <row r="165">
@@ -10548,7 +10548,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>17185.41</v>
+        <v>17252.49</v>
       </c>
     </row>
     <row r="166">
@@ -10609,7 +10609,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>6333.26</v>
+        <v>6357.98</v>
       </c>
     </row>
     <row r="167">
@@ -10670,7 +10670,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>18790.08</v>
+        <v>18694.89</v>
       </c>
     </row>
     <row r="168">
@@ -10731,7 +10731,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>16853.01</v>
+        <v>16767.64</v>
       </c>
     </row>
     <row r="169">
@@ -10792,7 +10792,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>277.47</v>
+        <v>278.06</v>
       </c>
     </row>
     <row r="170">
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>11594.73</v>
+        <v>11670.32</v>
       </c>
     </row>
     <row r="171">
@@ -10914,7 +10914,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>3236.78</v>
+        <v>3244.21</v>
       </c>
     </row>
     <row r="172">
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>6388.63</v>
+        <v>6374.73</v>
       </c>
     </row>
     <row r="173">
@@ -11036,7 +11036,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>12889.78</v>
+        <v>12815.17</v>
       </c>
     </row>
     <row r="174">
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>45114.24</v>
+        <v>44390.89</v>
       </c>
     </row>
     <row r="175">
@@ -11158,7 +11158,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>10741.66</v>
+        <v>10616.68</v>
       </c>
     </row>
     <row r="176">
@@ -11223,7 +11223,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>79556.94</v>
+        <v>78631.24000000001</v>
       </c>
     </row>
     <row r="177">
@@ -11284,7 +11284,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>9770.84</v>
+        <v>9716.67</v>
       </c>
     </row>
     <row r="178">
@@ -11345,7 +11345,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>52307.83</v>
+        <v>52017.84</v>
       </c>
     </row>
     <row r="179">
@@ -11406,7 +11406,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>11065.62</v>
+        <v>11011.21</v>
       </c>
     </row>
     <row r="180">
@@ -11467,7 +11467,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>23631.27</v>
+        <v>23515.08</v>
       </c>
     </row>
     <row r="181">
@@ -11528,7 +11528,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>214.83</v>
+        <v>213.77</v>
       </c>
     </row>
     <row r="182">
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>13213.21</v>
+        <v>13301.65</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/lib-gral-bdo-o-higgins.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/lib-gral-bdo-o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M182"/>
+  <dimension ref="A1:M197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2080-42040-CM25</t>
+          <t>2207-13-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>13928.32</v>
+        <v>9007.610000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2207-1194-CM25</t>
+          <t>2188-13-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>61.602.134-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>SERVICIO DE SALUD HOSPITAL COINCO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>11418.83</v>
+        <v>43584.88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1402-759-CM25</t>
+          <t>2080-17378-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1063.23</v>
+        <v>14147.68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1628-310-CM25</t>
+          <t>626788-14-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.980.040-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>12758.76</v>
+        <v>403.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1623-522-CM25</t>
+          <t>889473-350-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9615.85</v>
+        <v>7037.27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2107-1906-CM25</t>
+          <t>1529-199-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>69831.66</v>
+        <v>45400.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1626-220-CM25</t>
+          <t>2207-724-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6100.73</v>
+        <v>11450.97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3374-148-CM25</t>
+          <t>1622-692-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2115.06</v>
+        <v>21373.46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3374-155-CM25</t>
+          <t>598-169-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.513.000-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>41391.71</v>
+        <v>15862.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2568-2197-CM25</t>
+          <t>889473-1728-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4320.01</v>
+        <v>11345.39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1402-776-CM25</t>
+          <t>1622-892-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>11691.68</v>
+        <v>23744.63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1350767-104-CM25</t>
+          <t>2107-1642-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.981.210-7</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>63729.79</v>
+        <v>43913.76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1623-494-CM25</t>
+          <t>889473-1979-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>212.57</v>
+        <v>10958.35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3374-153-CM25</t>
+          <t>1402-664-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>4269.45</v>
+        <v>10399.98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1621-369-CM25</t>
+          <t>2107-1889-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.602.151-6</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>8144.9</v>
+        <v>73277.19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2205-235-CM25</t>
+          <t>2207-1194-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,22 +1444,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,18 +1484,18 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6350.92</v>
+        <v>11418.83</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1627-1836-SE25</t>
+          <t>2080-42040-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2239-2-LR21</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1538,24 +1538,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>89358.98</v>
+        <v>13928.32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1071580-34-CM25</t>
+          <t>1402-759-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1570,22 +1566,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>Dirección Regional de Gendarmeria - Rancagua</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1610,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>12115.26</v>
+        <v>1063.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1620-286-CM25</t>
+          <t>1628-310-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1631,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1641,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1671,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>10871.69</v>
+        <v>12758.76</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1624-291-CM25</t>
+          <t>1623-522-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1692,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1702,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.602.147-8</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1732,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>8953.59</v>
+        <v>9615.85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1622-1133-CM25</t>
+          <t>2107-1906-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1753,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1763,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1793,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>22604.95</v>
+        <v>69831.66</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1398-2657-CM25</t>
+          <t>1626-220-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1814,7 +1810,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1824,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1854,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3552.53</v>
+        <v>6100.73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1402-846-CM25</t>
+          <t>3374-148-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1875,7 +1871,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1885,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1915,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>4296.96</v>
+        <v>2115.06</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1402-845-CM25</t>
+          <t>3374-155-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1936,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1946,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1976,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1826.21</v>
+        <v>41391.71</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2080-53163-CM25</t>
+          <t>2568-2197-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1997,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2007,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2037,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>9453.32</v>
+        <v>4320.01</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1529-418-CM25</t>
+          <t>1402-776-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2058,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2068,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>Dirección Regional de Gendarmeria - Rancagua</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2098,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>48524.66</v>
+        <v>11691.68</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1624-319-CM25</t>
+          <t>1350767-104-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2119,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2129,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.602.147-8</t>
+          <t>61.981.210-7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+          <t>EJERCITO DE CHILE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2159,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>7286.58</v>
+        <v>63729.79</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2207-1221-CM25</t>
+          <t>1623-494-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2175,27 +2171,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2220,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>7940.88</v>
+        <v>212.57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1626-242-CM25</t>
+          <t>1621-369-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2236,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2251,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>61.602.151-6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2281,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5546.33</v>
+        <v>8144.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>905-299-CM25</t>
+          <t>3374-153-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2297,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2312,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2342,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1370.37</v>
+        <v>4269.45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1623-572-CM25</t>
+          <t>2205-235-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2358,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2373,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2403,28 +2399,28 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>217.52</v>
+        <v>6350.92</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1623-573-CM25</t>
+          <t>1627-1836-SE25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-2-LR21</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2434,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2457,20 +2453,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>12507.34</v>
+        <v>89358.98</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1628-368-CM25</t>
+          <t>1624-291-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.602.147-8</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>16303.99</v>
+        <v>8953.59</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2568-2265-CM25</t>
+          <t>1620-286-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2541,12 +2541,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2586,13 +2586,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2230.39</v>
+        <v>10871.69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1350767-123-CM25</t>
+          <t>1071580-34-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2602,27 +2602,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.981.210-7</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>60976.94</v>
+        <v>12115.26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3374-175-CM25</t>
+          <t>1398-2657-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2663,12 +2663,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>29733.84</v>
+        <v>3552.53</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2568-2286-CM25</t>
+          <t>1622-1133-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2769,13 +2769,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2290.01</v>
+        <v>22604.95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2568-2290-CM25</t>
+          <t>1402-845-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Dirección Regional de Gendarmeria - Rancagua</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2830,13 +2830,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>572.5</v>
+        <v>1826.21</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>889473-2773-CM25</t>
+          <t>2080-53163-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>10549.65</v>
+        <v>9453.32</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3810-7335-CM25</t>
+          <t>1529-418-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2952,13 +2952,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>25408.37</v>
+        <v>48524.66</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>615-100-CM25</t>
+          <t>1624-319-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.802.006-1</t>
+          <t>61.602.147-8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>770.12</v>
+        <v>7286.58</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2080-56569-CM25</t>
+          <t>1402-846-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>Dirección Regional de Gendarmeria - Rancagua</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3074,13 +3074,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>11522.15</v>
+        <v>4296.96</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1620-305-CM25</t>
+          <t>1626-242-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>14170.53</v>
+        <v>5546.33</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1398-2787-CM25</t>
+          <t>2207-1221-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3156,22 +3156,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3196,13 +3196,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1079.27</v>
+        <v>7940.88</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1402-884-CM25</t>
+          <t>905-299-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3227,12 +3227,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3257,13 +3257,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1648.53</v>
+        <v>1370.37</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1402-883-CM25</t>
+          <t>1623-572-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3318,13 +3318,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2857.46</v>
+        <v>217.52</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2205-286-CM25</t>
+          <t>1623-573-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3349,12 +3349,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3379,18 +3379,18 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>6460.71</v>
+        <v>12507.34</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1627-2086-SE25</t>
+          <t>1628-368-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2239-2-LR21</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3433,24 +3433,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>77201.42</v>
+        <v>16303.99</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1628-372-CM25</t>
+          <t>2568-2265-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3465,7 +3461,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3475,12 +3471,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3505,13 +3501,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>16573.85</v>
+        <v>2230.39</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1529-436-CM25</t>
+          <t>1350767-123-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3526,7 +3522,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3536,12 +3532,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.981.210-7</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>EJERCITO DE CHILE</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3566,13 +3562,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>50422.42</v>
+        <v>60976.94</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1622-1279-CM25</t>
+          <t>3374-175-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3587,7 +3583,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3597,12 +3593,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3627,13 +3623,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>23047.04</v>
+        <v>29733.84</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2207-1-CM26</t>
+          <t>2568-2290-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3643,27 +3639,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3688,13 +3684,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>9969.91</v>
+        <v>572.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2188-1-CM26</t>
+          <t>2568-2286-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3704,12 +3700,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3719,12 +3715,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.602.134-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL COINCO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3749,13 +3745,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>28840.89</v>
+        <v>2290.01</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1402-2-CM26</t>
+          <t>3810-7335-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3765,12 +3761,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3780,12 +3776,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3810,13 +3806,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1104.8</v>
+        <v>25408.37</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1626-1-CM26</t>
+          <t>889473-2773-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3826,12 +3822,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3841,12 +3837,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3871,13 +3867,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>6088.4</v>
+        <v>10549.65</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1402-8-CM26</t>
+          <t>1620-305-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3887,12 +3883,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3902,12 +3898,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3932,13 +3928,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>8920.41</v>
+        <v>14170.53</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1623-6-CM26</t>
+          <t>2080-56569-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3948,12 +3944,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3963,12 +3959,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3993,13 +3989,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>12823.73</v>
+        <v>11522.15</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1621-5-CM26</t>
+          <t>615-100-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4009,12 +4005,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4024,12 +4020,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.602.151-6</t>
+          <t>61.802.006-1</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
+          <t>Ministerio de Vivienda y Urbanismo</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4054,13 +4050,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>11814.15</v>
+        <v>770.12</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2207-41-CM26</t>
+          <t>1398-2787-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4070,27 +4066,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4115,13 +4111,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>11502.2</v>
+        <v>1079.27</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2080-409-CM26</t>
+          <t>2205-286-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4131,12 +4127,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4146,12 +4142,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4176,28 +4172,28 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>52449.85</v>
+        <v>6460.71</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1627-50-SE26</t>
+          <t>1402-884-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2239-2-LR21</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4207,12 +4203,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>Dirección Regional de Gendarmeria - Rancagua</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4230,24 +4226,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>76875.12</v>
+        <v>1648.53</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1402-14-CM26</t>
+          <t>1402-883-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4257,12 +4249,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4302,28 +4294,28 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3643.78</v>
+        <v>2857.46</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1402-15-CM26</t>
+          <t>1627-2086-SE25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-2-LR21</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4333,12 +4325,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4356,20 +4348,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1252.55</v>
+        <v>77201.42</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2205-7-CM26</t>
+          <t>1628-372-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4379,12 +4375,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4394,12 +4390,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4424,13 +4420,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>6739.81</v>
+        <v>16573.85</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1402-13-CM26</t>
+          <t>1529-436-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4440,12 +4436,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4455,12 +4451,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4485,13 +4481,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>11465</v>
+        <v>50422.42</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2107-170-CM26</t>
+          <t>1622-1279-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4501,12 +4497,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4516,12 +4512,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4546,13 +4542,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>36687.99</v>
+        <v>23047.04</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2568-8-CM26</t>
+          <t>2207-1-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4567,22 +4563,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4607,13 +4603,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1200.17</v>
+        <v>9969.91</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1620-21-CM26</t>
+          <t>2188-1-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4628,7 +4624,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4638,12 +4634,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>61.602.134-6</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL COINCO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4668,13 +4664,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>16078.96</v>
+        <v>28840.89</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>522-12-CM26</t>
+          <t>1402-2-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4689,7 +4685,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4699,12 +4695,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.602.152-4</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>Dirección Regional de Gendarmeria - Rancagua</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4729,13 +4725,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>25266.74</v>
+        <v>1104.8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1622-117-CM26</t>
+          <t>1626-1-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4750,7 +4746,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4760,12 +4756,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4790,13 +4786,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>26651.84</v>
+        <v>6088.4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3374-2-CM26</t>
+          <t>1623-6-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4811,7 +4807,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4821,12 +4817,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4851,13 +4847,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2899.66</v>
+        <v>12823.73</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1624-12-CM26</t>
+          <t>1402-8-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4872,7 +4868,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4882,12 +4878,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.602.147-8</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+          <t>Dirección Regional de Gendarmeria - Rancagua</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4912,13 +4908,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>10409.64</v>
+        <v>8920.41</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1529-38-CM26</t>
+          <t>1621-5-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4933,7 +4929,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4943,12 +4939,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.151-6</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4973,13 +4969,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>51393.29</v>
+        <v>11814.15</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1628-5-CM26</t>
+          <t>2207-41-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4994,22 +4990,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5034,13 +5030,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>12813.79</v>
+        <v>11502.2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1626-19-CM26</t>
+          <t>2080-409-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5050,12 +5046,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5065,12 +5061,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5095,28 +5091,28 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>7453.57</v>
+        <v>52449.85</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1402-37-CM26</t>
+          <t>1627-50-SE26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-2-LR21</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5126,12 +5122,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5149,20 +5145,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1151.38</v>
+        <v>76875.12</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1623-51-CM26</t>
+          <t>1402-15-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>Dirección Regional de Gendarmeria - Rancagua</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5217,13 +5217,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>13180.7</v>
+        <v>1252.55</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2207-118-CM26</t>
+          <t>1402-14-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5233,27 +5233,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>Dirección Regional de Gendarmeria - Rancagua</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5278,13 +5278,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>13150.55</v>
+        <v>3643.78</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>594965-14-CM26</t>
+          <t>2205-7-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5339,28 +5339,28 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>9216.700000000001</v>
+        <v>6739.81</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1627-229-SE26</t>
+          <t>1402-13-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2239-2-LR21</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>Dirección Regional de Gendarmeria - Rancagua</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5393,39 +5393,35 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>6313.63</v>
+        <v>11465</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1627-240-SE26</t>
+          <t>2107-170-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2239-2-LR21</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5435,12 +5431,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5458,24 +5454,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>110634.11</v>
+        <v>36687.99</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1620-47-CM26</t>
+          <t>522-12-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5485,12 +5477,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5500,12 +5492,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>61.602.152-4</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>HOSPITAL DE LITUECHE</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5530,13 +5522,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>16151.3</v>
+        <v>25266.74</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2205-28-CM26</t>
+          <t>2568-8-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5546,12 +5538,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5561,12 +5553,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5591,13 +5583,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>6779.38</v>
+        <v>1200.17</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1624-35-CM26</t>
+          <t>1620-21-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5607,12 +5599,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5622,12 +5614,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.602.147-8</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5652,13 +5644,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>9797.950000000001</v>
+        <v>16078.96</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1628-22-CM26</t>
+          <t>1622-117-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5668,12 +5660,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5683,12 +5675,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5713,13 +5705,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>13867.06</v>
+        <v>26651.84</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2107-413-CM26</t>
+          <t>3374-2-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5729,12 +5721,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5744,12 +5736,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5774,13 +5766,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>54312.66</v>
+        <v>2899.66</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2207-174-CM26</t>
+          <t>1624-12-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5790,27 +5782,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>61.602.147-8</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5835,13 +5827,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>13182.44</v>
+        <v>10409.64</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1529-58-CM26</t>
+          <t>1628-5-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5851,12 +5843,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5866,12 +5858,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5896,13 +5888,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>52806.6</v>
+        <v>12813.79</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2568-60-CM26</t>
+          <t>1529-38-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5912,12 +5904,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5927,12 +5919,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5957,13 +5949,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>3052.53</v>
+        <v>51393.29</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1622-288-CM26</t>
+          <t>1626-19-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5973,12 +5965,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5988,12 +5980,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6018,13 +6010,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>26394.01</v>
+        <v>7453.57</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1626-31-CM26</t>
+          <t>1402-37-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6034,12 +6026,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6049,12 +6041,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>Dirección Regional de Gendarmeria - Rancagua</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6079,13 +6071,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>5836.13</v>
+        <v>1151.38</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1623-91-CM26</t>
+          <t>1623-51-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6095,12 +6087,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6140,13 +6132,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>13240.39</v>
+        <v>13180.7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>626788-6-CM26</t>
+          <t>2207-118-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6156,27 +6148,27 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.980.040-0</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6201,13 +6193,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>446.2</v>
+        <v>13150.55</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1621-82-CM26</t>
+          <t>594965-14-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6217,12 +6209,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6232,12 +6224,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.602.151-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6262,28 +6254,28 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>11418.99</v>
+        <v>9216.700000000001</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3374-22-CM26</t>
+          <t>1627-229-SE26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-2-LR21</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6293,12 +6285,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6316,20 +6308,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2237.91</v>
+        <v>6313.63</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1627-369-SE26</t>
+          <t>1627-240-SE26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6339,12 +6335,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6388,13 +6384,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>79005.72</v>
+        <v>110634.11</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2205-40-CM26</t>
+          <t>1620-47-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6404,12 +6400,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6419,12 +6415,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6449,13 +6445,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>6423.65</v>
+        <v>16151.3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2107-497-CM26</t>
+          <t>2205-28-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6465,12 +6461,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6480,12 +6476,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6510,13 +6506,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>45863.66</v>
+        <v>6779.38</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1620-78-CM26</t>
+          <t>1624-35-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6526,12 +6522,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6541,12 +6537,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>61.602.147-8</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6571,13 +6567,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>10948.34</v>
+        <v>9797.950000000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1628-79-CM26</t>
+          <t>1628-22-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6587,12 +6583,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6632,13 +6628,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>13131.55</v>
+        <v>13867.06</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1193180-16-CM26</t>
+          <t>2107-413-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6648,12 +6644,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6663,12 +6659,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>60.511.060-6</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL LIBERTADOR BERNARDO  O´HIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6693,13 +6689,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1029.41</v>
+        <v>54312.66</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1529-88-CM26</t>
+          <t>2207-174-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6709,27 +6705,27 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6754,13 +6750,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>49453.98</v>
+        <v>13182.44</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2188-82-CM26</t>
+          <t>1529-58-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6770,12 +6766,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6785,12 +6781,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.602.134-6</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL COINCO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6815,13 +6811,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>38992.69</v>
+        <v>52806.6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1624-66-CM26</t>
+          <t>1622-288-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6836,7 +6832,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6846,12 +6842,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.602.147-8</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6876,13 +6872,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>10029.71</v>
+        <v>26394.01</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3374-30-CM26</t>
+          <t>2568-60-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6897,7 +6893,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6907,12 +6903,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6937,13 +6933,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>5367.28</v>
+        <v>3052.53</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1622-456-CM26</t>
+          <t>1623-91-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6953,12 +6949,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6968,12 +6964,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6998,13 +6994,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>23856.77</v>
+        <v>13240.39</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1339542-16-CM26</t>
+          <t>1626-31-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7014,27 +7010,27 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7059,13 +7055,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>5090.37</v>
+        <v>5836.13</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1626-58-CM26</t>
+          <t>626788-6-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7075,12 +7071,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7090,12 +7086,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>61.980.040-0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7120,13 +7116,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>6605.93</v>
+        <v>446.2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2207-264-CM26</t>
+          <t>1621-82-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7136,27 +7132,27 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>61.602.151-6</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7181,13 +7177,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>12253.55</v>
+        <v>11418.99</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1623-152-CM26</t>
+          <t>3374-22-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7197,12 +7193,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7212,12 +7208,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7242,28 +7238,28 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>13422.86</v>
+        <v>2237.91</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>5336-9-CM26</t>
+          <t>1627-369-SE26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-2-LR21</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7273,12 +7269,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>65.705.920-k</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7296,20 +7292,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1062.44</v>
+        <v>79005.72</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1621-109-CM26</t>
+          <t>2205-40-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7319,12 +7319,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7334,12 +7334,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.602.151-6</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7364,13 +7364,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>11702.37</v>
+        <v>6423.65</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2568-91-CM26</t>
+          <t>2107-497-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7395,12 +7395,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7425,13 +7425,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2974.83</v>
+        <v>45863.66</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1624-82-CM26</t>
+          <t>1620-78-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7441,12 +7441,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.602.147-8</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7486,13 +7486,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>10076.44</v>
+        <v>10948.34</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>889473-509-CM26</t>
+          <t>1628-79-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7547,13 +7547,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>6608.54</v>
+        <v>13131.55</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1350767-52-CM26</t>
+          <t>2188-82-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7563,12 +7563,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7578,12 +7578,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.981.210-7</t>
+          <t>61.602.134-6</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE</t>
+          <t>SERVICIO DE SALUD HOSPITAL COINCO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7608,13 +7608,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>4505.57</v>
+        <v>38992.69</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2205-56-CM26</t>
+          <t>1193180-16-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>60.511.060-6</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL LIBERTADOR BERNARDO  O´HIGGINS</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7669,13 +7669,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>6589.03</v>
+        <v>1029.41</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1620-91-CM26</t>
+          <t>1529-88-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7685,12 +7685,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7700,12 +7700,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7730,13 +7730,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>17871.87</v>
+        <v>49453.98</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1622-546-CM26</t>
+          <t>1624-66-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7761,12 +7761,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.602.147-8</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7791,28 +7791,28 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>25696.32</v>
+        <v>10029.71</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1627-549-SE26</t>
+          <t>3374-30-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2239-2-LR21</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7845,24 +7845,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>76349.73</v>
+        <v>5367.28</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2107-705-CM26</t>
+          <t>1622-456-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7877,7 +7873,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7887,12 +7883,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7917,13 +7913,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>46970.41</v>
+        <v>23856.77</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1529-132-CM26</t>
+          <t>1626-58-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7938,7 +7934,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7948,12 +7944,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7978,13 +7974,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>51398.12</v>
+        <v>6605.93</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>889473-601-CM26</t>
+          <t>1339542-16-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7994,27 +7990,27 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8039,13 +8035,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>9644.65</v>
+        <v>5090.37</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1626-80-CM26</t>
+          <t>2207-264-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8055,27 +8051,27 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8100,13 +8096,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>6188.99</v>
+        <v>12253.55</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>594965-60-CM26</t>
+          <t>1623-152-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8116,12 +8112,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8131,12 +8127,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8161,13 +8157,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1636.91</v>
+        <v>13422.86</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1628-134-CM26</t>
+          <t>1621-109-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8177,12 +8173,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8192,12 +8188,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.602.151-6</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8222,13 +8218,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>16568</v>
+        <v>11702.37</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2568-107-CM26</t>
+          <t>5336-9-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8238,12 +8234,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8253,12 +8249,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>65.705.920-k</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8283,13 +8279,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2889.46</v>
+        <v>1062.44</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1623-198-CM26</t>
+          <t>2568-91-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8299,12 +8295,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8314,12 +8310,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8344,13 +8340,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>13524.59</v>
+        <v>2974.83</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2207-378-CM26</t>
+          <t>1624-82-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8360,27 +8356,27 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>61.602.147-8</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8405,13 +8401,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>12641.88</v>
+        <v>10076.44</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1623-201-CM26</t>
+          <t>889473-509-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8421,12 +8417,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8436,12 +8432,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8466,13 +8462,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>335.48</v>
+        <v>6608.54</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>522-96-CM26</t>
+          <t>1350767-52-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8482,12 +8478,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8497,12 +8493,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.602.152-4</t>
+          <t>61.981.210-7</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>EJERCITO DE CHILE</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8527,13 +8523,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>10101.01</v>
+        <v>4505.57</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1621-147-CM26</t>
+          <t>2205-56-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8543,12 +8539,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8558,12 +8554,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.602.151-6</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8588,13 +8584,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>11606.06</v>
+        <v>6589.03</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2205-76-CM26</t>
+          <t>1622-546-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8604,12 +8600,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8619,12 +8615,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8649,13 +8645,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>6520.26</v>
+        <v>25696.32</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1529-152-CM26</t>
+          <t>1620-91-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8665,12 +8661,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8680,12 +8676,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8710,28 +8706,28 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>50601.66</v>
+        <v>17871.87</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1627-760-SE26</t>
+          <t>1529-132-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2239-2-LR21</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8741,12 +8737,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8764,39 +8760,35 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>80538.08</v>
+        <v>51398.12</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2107-958-CM26</t>
+          <t>1627-549-SE26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-2-LR21</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8806,12 +8798,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8829,20 +8821,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>46938.39</v>
+        <v>76349.73</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1628-185-CM26</t>
+          <t>2107-705-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8852,12 +8848,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8867,12 +8863,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8897,13 +8893,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>14528.55</v>
+        <v>46970.41</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1624-117-CM26</t>
+          <t>889473-601-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8918,7 +8914,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8928,12 +8924,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.602.147-8</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8958,13 +8954,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>9052.709999999999</v>
+        <v>9644.65</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1620-124-CM26</t>
+          <t>594965-60-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8979,7 +8975,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8989,12 +8985,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9019,13 +9015,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>16801.32</v>
+        <v>1636.91</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1622-719-CM26</t>
+          <t>1626-80-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9035,12 +9031,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9050,12 +9046,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9080,13 +9076,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>24701.34</v>
+        <v>6188.99</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2080-5028-CM26</t>
+          <t>1628-134-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9096,27 +9092,27 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9141,13 +9137,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>12092.38</v>
+        <v>16568</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2107-1024-CM26</t>
+          <t>2568-107-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9157,12 +9153,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9172,12 +9168,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9202,13 +9198,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>47037.22</v>
+        <v>2889.46</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1626-110-CM26</t>
+          <t>1623-198-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9218,12 +9214,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9233,12 +9229,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9263,13 +9259,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>6248.43</v>
+        <v>13524.59</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>889473-835-CM26</t>
+          <t>2207-378-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9279,27 +9275,27 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9324,13 +9320,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>12832.64</v>
+        <v>12641.88</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1623-239-CM26</t>
+          <t>1623-201-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9340,12 +9336,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9385,13 +9381,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>13419.51</v>
+        <v>335.48</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2207-460-CM26</t>
+          <t>522-96-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9401,12 +9397,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9416,12 +9412,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>61.602.152-4</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>HOSPITAL DE LITUECHE</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9446,13 +9442,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>12631.43</v>
+        <v>10101.01</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1211-19-CM26</t>
+          <t>2205-76-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9462,12 +9458,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9477,12 +9473,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>60.901.008-8</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION VI REGION</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9507,13 +9503,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>488.4</v>
+        <v>6520.26</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3374-76-CM26</t>
+          <t>1621-147-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9523,12 +9519,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9538,12 +9534,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.602.151-6</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9568,13 +9564,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>6547.43</v>
+        <v>11606.06</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3374-73-CM26</t>
+          <t>1529-152-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9584,12 +9580,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9599,12 +9595,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9629,13 +9625,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>3273.71</v>
+        <v>50601.66</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2205-86-CM26</t>
+          <t>1628-185-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9645,12 +9641,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9660,12 +9656,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9690,28 +9686,28 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>6414.95</v>
+        <v>14528.55</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2062-32-CM26</t>
+          <t>1627-760-SE26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-2-LR21</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9721,12 +9717,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>60.902.051-2</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación de Cachapoal</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9744,20 +9740,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>99.01000000000001</v>
+        <v>80538.08</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1620-134-CM26</t>
+          <t>2107-958-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9767,12 +9767,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9782,12 +9782,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9812,13 +9812,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>16679.05</v>
+        <v>46938.39</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2188-176-CM26</t>
+          <t>1624-117-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9843,12 +9843,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>61.602.134-6</t>
+          <t>61.602.147-8</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL COINCO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9873,13 +9873,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>20303.88</v>
+        <v>9052.709999999999</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1623-248-CM26</t>
+          <t>1620-124-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9889,12 +9889,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9934,18 +9934,18 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>565.98</v>
+        <v>16801.32</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2080-5899-CM26</t>
+          <t>1622-719-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9955,22 +9955,22 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9995,18 +9995,18 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>13304.02</v>
+        <v>24701.34</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1529-188-CM26</t>
+          <t>2080-5028-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10016,22 +10016,22 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10056,18 +10056,18 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>52146.81</v>
+        <v>12092.38</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>889473-1013-CM26</t>
+          <t>2107-1024-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10087,12 +10087,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10117,18 +10117,18 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>11231.36</v>
+        <v>47037.22</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1628-208-CM26</t>
+          <t>1626-110-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10178,18 +10178,18 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>16279.22</v>
+        <v>6248.43</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1627-886-SE26</t>
+          <t>889473-835-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2239-2-LR21</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10209,12 +10209,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10232,29 +10232,25 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>80771.59</v>
+        <v>12832.64</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1622-838-CM26</t>
+          <t>1623-239-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10264,7 +10260,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10274,12 +10270,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10304,18 +10300,18 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>23992.06</v>
+        <v>13419.51</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1623-284-CM26</t>
+          <t>2207-460-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10325,7 +10321,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10335,12 +10331,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10365,28 +10361,28 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>13023.25</v>
+        <v>12631.43</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1624-146-CM26</t>
+          <t>1211-19-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10396,12 +10392,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.602.147-8</t>
+          <t>60.901.008-8</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION VI REGION</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10426,28 +10422,28 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>9686.610000000001</v>
+        <v>488.4</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>522-126-CM26</t>
+          <t>3374-73-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10457,12 +10453,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.602.152-4</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10487,28 +10483,28 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>9758.01</v>
+        <v>3273.71</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>522-130-CM26</t>
+          <t>2205-86-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10518,12 +10514,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>61.602.152-4</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10548,28 +10544,28 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>17252.49</v>
+        <v>6414.95</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1626-130-CM26</t>
+          <t>3374-76-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10579,12 +10575,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10609,43 +10605,43 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>6357.98</v>
+        <v>6547.43</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2207-516-CM26</t>
+          <t>2062-32-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>60.902.051-2</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>Departamento Provincial de Educación de Cachapoal</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10670,43 +10666,43 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>18694.89</v>
+        <v>99.01000000000001</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>897-35-CM26</t>
+          <t>1620-134-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10731,28 +10727,28 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>16767.64</v>
+        <v>16679.05</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1626-131-CM26</t>
+          <t>2188-176-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10762,12 +10758,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>61.602.134-6</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>SERVICIO DE SALUD HOSPITAL COINCO</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10792,28 +10788,28 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>278.06</v>
+        <v>20303.88</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1621-197-CM26</t>
+          <t>1623-248-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10823,12 +10819,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.602.151-6</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10853,13 +10849,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>11670.32</v>
+        <v>565.98</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>615-37-CM26</t>
+          <t>2080-5899-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10869,27 +10865,27 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.802.006-1</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10914,13 +10910,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>3244.21</v>
+        <v>13304.02</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2205-101-CM26</t>
+          <t>1529-188-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10930,12 +10926,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10945,12 +10941,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10975,13 +10971,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>6374.73</v>
+        <v>52146.81</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1628-223-CM26</t>
+          <t>889473-1013-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10991,12 +10987,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -11006,12 +11002,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11036,13 +11032,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>12815.17</v>
+        <v>11231.36</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2107-1495-CM26</t>
+          <t>1628-208-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11052,12 +11048,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -11067,12 +11063,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11097,13 +11093,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>44390.89</v>
+        <v>16279.22</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1620-160-CM26</t>
+          <t>1622-838-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11113,12 +11109,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11128,12 +11124,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11158,13 +11154,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>10616.68</v>
+        <v>23992.06</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1627-1057-SE26</t>
+          <t>1627-886-SE26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11174,12 +11170,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -11223,13 +11219,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>78631.24000000001</v>
+        <v>80771.59</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1624-176-CM26</t>
+          <t>1623-284-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11239,12 +11235,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -11254,12 +11250,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.602.147-8</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11284,13 +11280,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>9716.67</v>
+        <v>13023.25</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1529-211-CM26</t>
+          <t>1624-146-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11305,7 +11301,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11315,12 +11311,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.147-8</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11330,12 +11326,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11345,13 +11341,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>52017.84</v>
+        <v>9686.610000000001</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>889473-1275-CM26</t>
+          <t>522-126-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11366,7 +11362,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -11376,12 +11372,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.602.152-4</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>HOSPITAL DE LITUECHE</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11406,13 +11402,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>11011.21</v>
+        <v>9758.01</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1622-998-CM26</t>
+          <t>522-130-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11427,7 +11423,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11437,12 +11433,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.602.152-4</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>HOSPITAL DE LITUECHE</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11467,13 +11463,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>23515.08</v>
+        <v>17252.49</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1079563-312-CM26</t>
+          <t>1626-130-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11488,22 +11484,22 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>61.978.680-7</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11513,12 +11509,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -11528,13 +11524,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>213.77</v>
+        <v>6357.98</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2080-7563-CM26</t>
+          <t>2207-516-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11549,7 +11545,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11559,12 +11555,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11589,6 +11585,925 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
+        <v>18694.89</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>897-35-CM26</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="n">
+        <v>16767.64</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>1626-131-CM26</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>61.602.150-8</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Hospital de Lolol</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="n">
+        <v>278.06</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>1621-197-CM26</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>61.602.151-6</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE MARCHIGUE</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="n">
+        <v>11670.32</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>615-37-CM26</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>61.802.006-1</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Ministerio de Vivienda y Urbanismo</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="n">
+        <v>3244.21</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2205-101-CM26</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>61.602.143-5</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="n">
+        <v>6374.73</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>1628-223-CM26</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>61.602.132-k</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="n">
+        <v>12815.17</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2107-1495-CM26</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>61.602.148-6</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="n">
+        <v>44390.89</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>1620-160-CM26</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>61.602.146-k</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="n">
+        <v>10616.68</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>1627-1057-SE26</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2239-2-LR21</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>61.602.145-1</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="n">
+        <v>78631.24000000001</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>1624-176-CM26</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>61.602.147-8</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE NANCAGUA</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="n">
+        <v>9716.67</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>1529-211-CM26</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>61.602.140-0</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="n">
+        <v>52017.84</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>1079563-312-CM26</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>61.978.680-7</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS VI ZONA</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="n">
+        <v>213.77</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>889473-1275-CM26</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>61.980.530-5</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="n">
+        <v>11011.21</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>1622-998-CM26</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>61.602.141-9</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="n">
+        <v>23515.08</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2080-7563-CM26</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>61.602.138-9</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="n">
         <v>13301.65</v>
       </c>
     </row>
